--- a/Database_Jadwal_Produksi.xlsx
+++ b/Database_Jadwal_Produksi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6590"/>
+    <workbookView windowWidth="18350" windowHeight="6590" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="411">
   <si>
     <t>DIPAKSA MENIKAH - MASTER SCHEDULE (ALL 70 SUB-SCENES)</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Est. Time</t>
   </si>
   <si>
-    <t>SET CATEGORY: EKSTERIOR &amp; LOKASI PUBLIK</t>
+    <t>TAMAN, JALANAN, DAN BANDARA</t>
   </si>
   <si>
     <t>01</t>
@@ -144,7 +144,7 @@
     <t>Pernikahan batal. Bambang murka dan terkena serangan jantung.</t>
   </si>
   <si>
-    <t>SET CATEGORY: AREA SEKOLAH &amp; EXPO</t>
+    <t>AREA SEKOLAH &amp; EXPO</t>
   </si>
   <si>
     <t>03</t>
@@ -234,7 +234,7 @@
     <t>10:00 - 11:30</t>
   </si>
   <si>
-    <t>SET CATEGORY: RUMAH SAKIT &amp; LORONG VIP</t>
+    <t>RUMAH SAKIT</t>
   </si>
   <si>
     <t>06</t>
@@ -381,7 +381,7 @@
     <t>Ramli mengaku hancur terlilit utang Rp3,5 Miliar.</t>
   </si>
   <si>
-    <t>SET CATEGORY: LOKASI LAINNYA</t>
+    <t>RESTORAN RAMLI</t>
   </si>
   <si>
     <t>16</t>
@@ -402,6 +402,9 @@
     <t>Flashback: Ramli tertipu investasi franchise.</t>
   </si>
   <si>
+    <t>KANTOR (KANTOR RICKO, KANTOR HENDRA DAN BANK)</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
@@ -459,7 +462,7 @@
     <t>Montage: Ramli stres di restoran sepi.</t>
   </si>
   <si>
-    <t>SET CATEGORY: RUMAH RAMLI / INTAN</t>
+    <t>RUMAH RAMLI / INTAN</t>
   </si>
   <si>
     <t>17c</t>
@@ -579,6 +582,9 @@
     <t>Intan kabur lewat jendela ke rumah Melly.</t>
   </si>
   <si>
+    <t>SET MOBIL</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
@@ -675,6 +681,9 @@
     <t>Adit membawakan roti untuk Intan.</t>
   </si>
   <si>
+    <t>RUMAH RICKO - KAMAR RICKO</t>
+  </si>
+  <si>
     <t>32</t>
   </si>
   <si>
@@ -690,6 +699,9 @@
     <t>Ricko melihat IG Stories Rossa dan unfollow.</t>
   </si>
   <si>
+    <t>LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
+  </si>
+  <si>
     <t>33</t>
   </si>
   <si>
@@ -1159,6 +1171,9 @@
   </si>
   <si>
     <t>DIPAKSA MENIKAH - DAY 1 SHOOTING SCHEDULE (SCHOOL, EXPO &amp; PUBLIC SETS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREA SEKOLAH &amp; EXPO				</t>
   </si>
   <si>
     <t>DIPAKSA MENIKAH - DAY 2 SHOOTING SCHEDULE (HOSPITAL &amp; VIP ROOMS)</t>
@@ -1261,7 +1276,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1300,13 +1315,6 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1795,28 +1803,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1825,118 +1836,115 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3162,7 +3170,7 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:11">
       <c r="A32" s="10" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3180,34 +3188,34 @@
         <v>20</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:11">
@@ -3215,34 +3223,34 @@
         <v>21</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K34" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:11">
@@ -3265,39 +3273,39 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:11">
       <c r="A37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3315,34 +3323,34 @@
         <v>23</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:11">
@@ -3365,7 +3373,7 @@
         <v>24</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>23</v>
@@ -3374,7 +3382,7 @@
         <v>69</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>92</v>
@@ -3389,10 +3397,10 @@
         <v>42</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:11">
@@ -3415,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>30</v>
@@ -3427,10 +3435,10 @@
         <v>31</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>59</v>
@@ -3439,15 +3447,15 @@
         <v>42</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:11">
       <c r="A43" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
@@ -3465,34 +3473,34 @@
         <v>26</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1" spans="1:11">
@@ -3500,34 +3508,34 @@
         <v>27</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:11">
@@ -3550,13 +3558,13 @@
         <v>28</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>31</v>
@@ -3565,19 +3573,19 @@
         <v>92</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1" spans="1:11">
@@ -3585,13 +3593,13 @@
         <v>29</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>56</v>
@@ -3603,21 +3611,21 @@
         <v>113</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:11">
       <c r="A49" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -3635,39 +3643,39 @@
         <v>30</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:11">
       <c r="A51" s="10" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -3685,39 +3693,39 @@
         <v>31</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:11">
       <c r="A53" s="10" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
@@ -3735,34 +3743,34 @@
         <v>32</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:11">
@@ -3785,34 +3793,34 @@
         <v>33</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1" spans="1:11">
@@ -3820,34 +3828,34 @@
         <v>34</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1" spans="1:11">
@@ -3855,34 +3863,34 @@
         <v>35</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:11">
@@ -3905,13 +3913,13 @@
         <v>36</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>31</v>
@@ -3920,19 +3928,19 @@
         <v>92</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:11">
@@ -3955,7 +3963,7 @@
         <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>30</v>
@@ -3964,30 +3972,30 @@
         <v>14</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F62" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="K62" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K62" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:11">
       <c r="A63" s="10" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -4005,7 +4013,7 @@
         <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>23</v>
@@ -4017,27 +4025,27 @@
         <v>15</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:11">
       <c r="A65" s="10" t="s">
-        <v>12</v>
+        <v>222</v>
       </c>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
@@ -4055,7 +4063,7 @@
         <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>30</v>
@@ -4067,22 +4075,22 @@
         <v>15</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:11">
@@ -4105,7 +4113,7 @@
         <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>23</v>
@@ -4117,27 +4125,27 @@
         <v>31</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:11">
       <c r="A69" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -4155,34 +4163,34 @@
         <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J70" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K70" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1" spans="1:11">
@@ -4190,39 +4198,39 @@
         <v>42</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:11">
       <c r="A72" s="10" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
@@ -4240,34 +4248,34 @@
         <v>43</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:11">
@@ -4290,39 +4298,39 @@
         <v>44</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:11">
       <c r="A76" s="10" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
@@ -4340,7 +4348,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>23</v>
@@ -4352,22 +4360,22 @@
         <v>56</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I77" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:11">
@@ -4390,7 +4398,7 @@
         <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>23</v>
@@ -4402,22 +4410,22 @@
         <v>31</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1" spans="1:11">
@@ -4425,7 +4433,7 @@
         <v>47</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>23</v>
@@ -4437,22 +4445,22 @@
         <v>56</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="81" ht="32" customHeight="1" spans="1:11">
@@ -4460,7 +4468,7 @@
         <v>48</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>23</v>
@@ -4472,22 +4480,22 @@
         <v>31</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="82" ht="32" customHeight="1" spans="1:11">
@@ -4495,7 +4503,7 @@
         <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>23</v>
@@ -4507,22 +4515,22 @@
         <v>31</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I82" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="K82" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1" spans="1:11">
@@ -4530,7 +4538,7 @@
         <v>50</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>23</v>
@@ -4542,27 +4550,27 @@
         <v>56</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:11">
       <c r="A84" s="10" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
@@ -4580,39 +4588,39 @@
         <v>51</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:11">
       <c r="A86" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
@@ -4630,34 +4638,34 @@
         <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1" spans="1:11">
@@ -4665,34 +4673,34 @@
         <v>53</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H88" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="K88" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:11">
@@ -4700,34 +4708,34 @@
         <v>54</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="90" ht="32" customHeight="1" spans="1:11">
@@ -4735,34 +4743,34 @@
         <v>55</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I90" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:11">
@@ -4770,34 +4778,34 @@
         <v>56</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1" spans="1:11">
@@ -4805,34 +4813,34 @@
         <v>57</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I92" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J92" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="K92" s="5" t="s">
         <v>312</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="93" ht="32" customHeight="1" spans="1:11">
@@ -4840,34 +4848,34 @@
         <v>58</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" ht="32" customHeight="1" spans="1:11">
@@ -4875,7 +4883,7 @@
         <v>59</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>23</v>
@@ -4887,27 +4895,27 @@
         <v>56</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:11">
       <c r="A95" s="10" t="s">
-        <v>12</v>
+        <v>222</v>
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
@@ -4925,34 +4933,34 @@
         <v>60</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="97" ht="32" customHeight="1" spans="1:11">
@@ -4960,39 +4968,39 @@
         <v>61</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H97" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:11">
       <c r="A98" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
@@ -5010,7 +5018,7 @@
         <v>62</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>23</v>
@@ -5022,22 +5030,22 @@
         <v>15</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" ht="32" customHeight="1" spans="1:11">
@@ -5045,7 +5053,7 @@
         <v>63</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>23</v>
@@ -5057,22 +5065,22 @@
         <v>56</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:11">
@@ -5080,7 +5088,7 @@
         <v>64</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>23</v>
@@ -5092,27 +5100,27 @@
         <v>56</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:11">
       <c r="A102" s="10" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
@@ -5130,7 +5138,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>23</v>
@@ -5142,22 +5150,22 @@
         <v>31</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:11">
@@ -5180,7 +5188,7 @@
         <v>66</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>30</v>
@@ -5192,22 +5200,22 @@
         <v>31</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" ht="32" customHeight="1" spans="1:11">
@@ -5215,7 +5223,7 @@
         <v>67</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>23</v>
@@ -5227,22 +5235,22 @@
         <v>31</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="107" ht="32" customHeight="1" spans="1:11">
@@ -5250,7 +5258,7 @@
         <v>68</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>30</v>
@@ -5262,27 +5270,27 @@
         <v>31</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:11">
       <c r="A108" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -5300,34 +5308,34 @@
         <v>69</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H109" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="K109" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="I109" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="K109" s="3" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="110" ht="32" customHeight="1" spans="1:11">
@@ -5335,34 +5343,34 @@
         <v>70</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5413,7 +5421,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:J47"/>
+  <dimension ref="A2:J50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5430,7 +5438,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:10">
@@ -5545,7 +5553,7 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>37</v>
+        <v>380</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -5829,7 +5837,7 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:10">
       <c r="A18" s="10" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5846,31 +5854,31 @@
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:10">
@@ -5878,31 +5886,31 @@
         <v>12</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:10">
@@ -5924,36 +5932,36 @@
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:10">
       <c r="A23" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5970,36 +5978,36 @@
         <v>14</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:10">
       <c r="A25" s="10" t="s">
-        <v>37</v>
+        <v>380</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6016,7 +6024,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>30</v>
@@ -6028,10 +6036,10 @@
         <v>31</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>59</v>
@@ -6040,12 +6048,12 @@
         <v>42</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:10">
       <c r="A27" s="10" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6062,535 +6070,577 @@
         <v>16</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:10">
-      <c r="A29" s="3">
+      <c r="A29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:10">
+      <c r="A30" s="3">
         <v>17</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="F30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1" spans="1:10">
-      <c r="A30" s="5">
+      <c r="H30" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:10">
+      <c r="A31" s="5">
         <v>18</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B31" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="D31" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:10">
-      <c r="A31" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
+      <c r="H31" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:10">
-      <c r="A32" s="5">
+      <c r="A32" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:10">
+      <c r="A33" s="5">
         <v>19</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="B33" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="H32" s="6" t="s">
+      <c r="E33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="1:10">
-      <c r="A33" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
+      <c r="H33" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:10">
-      <c r="A34" s="5">
+      <c r="A34" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:10">
+      <c r="A35" s="5">
         <v>20</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="B35" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J34" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:10">
-      <c r="A35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
+      <c r="G35" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1" spans="1:10">
-      <c r="A36" s="5">
+      <c r="A36" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:10">
+      <c r="A37" s="5">
         <v>21</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="B37" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="H36" s="6" t="s">
+      <c r="F37" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1" spans="1:10">
+      <c r="A38" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:10">
+      <c r="A39" s="5">
+        <v>22</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1" spans="1:10">
+      <c r="A40" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" ht="32" customHeight="1" spans="1:10">
+      <c r="A41" s="5">
+        <v>23</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="1:10">
+      <c r="A42" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="I36" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="1:10">
-      <c r="A37" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" ht="32" customHeight="1" spans="1:10">
-      <c r="A38" s="5">
-        <v>22</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1" spans="1:10">
-      <c r="A39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" ht="32" customHeight="1" spans="1:10">
-      <c r="A40" s="5">
-        <v>23</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1" spans="1:10">
-      <c r="A41" s="3">
-        <v>24</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1" spans="1:10">
-      <c r="A42" s="5">
-        <v>25</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>333</v>
-      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="32" customHeight="1" spans="1:10">
       <c r="A43" s="3">
+        <v>24</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1" spans="1:10">
+      <c r="A44" s="5">
+        <v>25</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:10">
+      <c r="A45" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:10">
+      <c r="A46" s="3">
         <v>26</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B46" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1" spans="1:10">
-      <c r="A44" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="45" ht="32" customHeight="1" spans="1:10">
-      <c r="A45" s="3">
+      <c r="F46" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1" spans="1:10">
+      <c r="A47" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" ht="32" customHeight="1" spans="1:10">
+      <c r="A48" s="3">
         <v>27</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B48" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1" spans="1:10">
-      <c r="A46" s="5">
+      <c r="F48" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1" spans="1:10">
+      <c r="A49" s="5">
         <v>28</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="B49" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1" spans="1:10">
-      <c r="A47" s="3">
+      <c r="F49" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="3">
         <v>29</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B50" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>363</v>
+      <c r="F50" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A8:J8"/>
@@ -6600,12 +6650,15 @@
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A47:J47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6633,7 +6686,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -6971,7 +7024,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>23</v>
@@ -6980,7 +7033,7 @@
         <v>69</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>92</v>
@@ -6995,7 +7048,7 @@
         <v>42</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>66</v>
@@ -7006,13 +7059,13 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>31</v>
@@ -7021,16 +7074,16 @@
         <v>92</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>66</v>
@@ -7041,13 +7094,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>56</v>
@@ -7059,13 +7112,13 @@
         <v>113</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>66</v>
@@ -7091,31 +7144,31 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>90</v>
@@ -7141,13 +7194,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>31</v>
@@ -7156,16 +7209,16 @@
         <v>92</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>90</v>
@@ -7176,31 +7229,31 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>90</v>
@@ -7211,7 +7264,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
@@ -7223,19 +7276,19 @@
         <v>31</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>90</v>
@@ -7246,7 +7299,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
@@ -7258,19 +7311,19 @@
         <v>56</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>107</v>
@@ -7281,7 +7334,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
@@ -7293,19 +7346,19 @@
         <v>31</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>107</v>
@@ -7316,7 +7369,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
@@ -7328,19 +7381,19 @@
         <v>31</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>107</v>
@@ -7351,7 +7404,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>23</v>
@@ -7363,19 +7416,19 @@
         <v>56</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>107</v>
@@ -7414,7 +7467,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -7504,7 +7557,7 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -7522,31 +7575,31 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>21</v>
@@ -7557,31 +7610,31 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>21</v>
@@ -7592,31 +7645,31 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>45</v>
@@ -7624,7 +7677,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:11">
       <c r="A11" s="10" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -7642,31 +7695,31 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>113</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>45</v>
@@ -7674,7 +7727,7 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:11">
       <c r="A13" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7692,31 +7745,31 @@
         <v>6</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>45</v>
@@ -7727,31 +7780,31 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>45</v>
@@ -7759,7 +7812,7 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:11">
       <c r="A16" s="10" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7777,31 +7830,31 @@
         <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>66</v>
@@ -7812,31 +7865,31 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>66</v>
@@ -7844,7 +7897,7 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:11">
       <c r="A19" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7862,31 +7915,31 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>66</v>
@@ -7897,31 +7950,31 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>66</v>
@@ -7932,31 +7985,31 @@
         <v>12</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>90</v>
@@ -7967,31 +8020,31 @@
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>90</v>
@@ -8002,31 +8055,31 @@
         <v>14</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>90</v>
@@ -8037,31 +8090,31 @@
         <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>90</v>
@@ -8072,31 +8125,31 @@
         <v>16</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>107</v>
@@ -8107,7 +8160,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>23</v>
@@ -8119,19 +8172,19 @@
         <v>56</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>107</v>
@@ -8142,7 +8195,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>23</v>
@@ -8154,19 +8207,19 @@
         <v>15</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>107</v>
@@ -8177,7 +8230,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>23</v>
@@ -8189,19 +8242,19 @@
         <v>56</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>107</v>
@@ -8212,7 +8265,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>23</v>
@@ -8224,22 +8277,22 @@
         <v>56</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:11">
@@ -8247,34 +8300,34 @@
         <v>21</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:11">
@@ -8282,34 +8335,34 @@
         <v>22</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -8342,148 +8395,148 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C10" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D10" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E10" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5">
       <c r="A11" s="8" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B11" s="9">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5">
       <c r="A12" s="8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C12" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E12" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" t="s">
         <v>405</v>
       </c>
-      <c r="C13" t="s">
-        <v>400</v>
-      </c>
       <c r="D13" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E13" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/Database_Jadwal_Produksi.xlsx
+++ b/Database_Jadwal_Produksi.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="412">
   <si>
     <t>DIPAKSA MENIKAH - MASTER SCHEDULE (ALL 70 SUB-SCENES)</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Est. Time</t>
   </si>
   <si>
-    <t>TAMAN, JALANAN, DAN BANDARA</t>
+    <t>SET CATEGORY : TAMAN, JALANAN, DAN BANDARA</t>
   </si>
   <si>
     <t>01</t>
@@ -144,7 +144,7 @@
     <t>Pernikahan batal. Bambang murka dan terkena serangan jantung.</t>
   </si>
   <si>
-    <t>AREA SEKOLAH &amp; EXPO</t>
+    <t>SET CATEGORY : AREA SEKOLAH &amp; EXPO</t>
   </si>
   <si>
     <t>03</t>
@@ -234,7 +234,7 @@
     <t>10:00 - 11:30</t>
   </si>
   <si>
-    <t>RUMAH SAKIT</t>
+    <t>SET CATEGORY : RUMAH SAKIT</t>
   </si>
   <si>
     <t>06</t>
@@ -381,7 +381,7 @@
     <t>Ramli mengaku hancur terlilit utang Rp3,5 Miliar.</t>
   </si>
   <si>
-    <t>RESTORAN RAMLI</t>
+    <t>SET CATEGORY : RESTORAN RAMLI</t>
   </si>
   <si>
     <t>16</t>
@@ -402,7 +402,7 @@
     <t>Flashback: Ramli tertipu investasi franchise.</t>
   </si>
   <si>
-    <t>KANTOR (KANTOR RICKO, KANTOR HENDRA DAN BANK)</t>
+    <t>SET CATEGORY : KANTOR RICKO, KANTOR HENDRA DAN BANK</t>
   </si>
   <si>
     <t>17</t>
@@ -462,7 +462,7 @@
     <t>Montage: Ramli stres di restoran sepi.</t>
   </si>
   <si>
-    <t>RUMAH RAMLI / INTAN</t>
+    <t>SET CATEGORY : RUMAH RAMLI / INTAN</t>
   </si>
   <si>
     <t>17c</t>
@@ -582,7 +582,7 @@
     <t>Intan kabur lewat jendela ke rumah Melly.</t>
   </si>
   <si>
-    <t>SET MOBIL</t>
+    <t>SET CATEGORY : SET MOBIL</t>
   </si>
   <si>
     <t>25</t>
@@ -681,7 +681,7 @@
     <t>Adit membawakan roti untuk Intan.</t>
   </si>
   <si>
-    <t>RUMAH RICKO - KAMAR RICKO</t>
+    <t>SET CATEGORY : RUMAH RICKO - KAMAR RICKO</t>
   </si>
   <si>
     <t>32</t>
@@ -699,7 +699,7 @@
     <t>Ricko melihat IG Stories Rossa dan unfollow.</t>
   </si>
   <si>
-    <t>LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
+    <t>SET CATEGORY : LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
   </si>
   <si>
     <t>33</t>
@@ -771,6 +771,9 @@
     <t>Montage: Intan dirias dengan kebaya pengantin.</t>
   </si>
   <si>
+    <t>SET CATEGORY : KANTOR (KANTOR RICKO, KANTOR HENDRA DAN BANK)</t>
+  </si>
+  <si>
     <t>36a</t>
   </si>
   <si>
@@ -1173,7 +1176,19 @@
     <t>DIPAKSA MENIKAH - DAY 1 SHOOTING SCHEDULE (SCHOOL, EXPO &amp; PUBLIC SETS)</t>
   </si>
   <si>
-    <t xml:space="preserve">AREA SEKOLAH &amp; EXPO				</t>
+    <r>
+      <t>SET CATEGORY : AREA SEKOLAH &amp; EXPO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF2C3E50"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">				</t>
+    </r>
   </si>
   <si>
     <t>DIPAKSA MENIKAH - DAY 2 SHOOTING SCHEDULE (HOSPITAL &amp; VIP ROOMS)</t>
@@ -1276,7 +1291,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1459,6 +1474,13 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -4230,7 +4252,7 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:11">
       <c r="A72" s="10" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
@@ -4248,7 +4270,7 @@
         <v>43</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>125</v>
@@ -4260,19 +4282,19 @@
         <v>15</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>220</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>235</v>
@@ -4298,7 +4320,7 @@
         <v>44</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>125</v>
@@ -4310,22 +4332,22 @@
         <v>15</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:11">
@@ -4348,7 +4370,7 @@
         <v>45</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>23</v>
@@ -4360,22 +4382,22 @@
         <v>56</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:11">
@@ -4398,7 +4420,7 @@
         <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>23</v>
@@ -4410,22 +4432,22 @@
         <v>31</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1" spans="1:11">
@@ -4433,7 +4455,7 @@
         <v>47</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>23</v>
@@ -4445,22 +4467,22 @@
         <v>56</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" ht="32" customHeight="1" spans="1:11">
@@ -4468,7 +4490,7 @@
         <v>48</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>23</v>
@@ -4480,22 +4502,22 @@
         <v>31</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" ht="32" customHeight="1" spans="1:11">
@@ -4503,7 +4525,7 @@
         <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>23</v>
@@ -4515,22 +4537,22 @@
         <v>31</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1" spans="1:11">
@@ -4538,7 +4560,7 @@
         <v>50</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>23</v>
@@ -4550,22 +4572,22 @@
         <v>56</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:11">
@@ -4588,7 +4610,7 @@
         <v>51</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>23</v>
@@ -4600,7 +4622,7 @@
         <v>15</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>42</v>
@@ -4612,10 +4634,10 @@
         <v>42</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:11">
@@ -4638,7 +4660,7 @@
         <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>30</v>
@@ -4650,22 +4672,22 @@
         <v>15</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1" spans="1:11">
@@ -4673,7 +4695,7 @@
         <v>53</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>30</v>
@@ -4685,22 +4707,22 @@
         <v>15</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:11">
@@ -4708,7 +4730,7 @@
         <v>54</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>23</v>
@@ -4720,22 +4742,22 @@
         <v>56</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" ht="32" customHeight="1" spans="1:11">
@@ -4743,7 +4765,7 @@
         <v>55</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>23</v>
@@ -4758,7 +4780,7 @@
         <v>163</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>196</v>
@@ -4767,10 +4789,10 @@
         <v>42</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:11">
@@ -4778,7 +4800,7 @@
         <v>56</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>23</v>
@@ -4790,22 +4812,22 @@
         <v>149</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1" spans="1:11">
@@ -4813,7 +4835,7 @@
         <v>57</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>23</v>
@@ -4822,13 +4844,13 @@
         <v>174</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>163</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>196</v>
@@ -4837,10 +4859,10 @@
         <v>42</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="93" ht="32" customHeight="1" spans="1:11">
@@ -4848,7 +4870,7 @@
         <v>58</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>23</v>
@@ -4860,22 +4882,22 @@
         <v>15</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="94" ht="32" customHeight="1" spans="1:11">
@@ -4883,7 +4905,7 @@
         <v>59</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>23</v>
@@ -4895,22 +4917,22 @@
         <v>56</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:11">
@@ -4933,7 +4955,7 @@
         <v>60</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>125</v>
@@ -4945,22 +4967,22 @@
         <v>127</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97" ht="32" customHeight="1" spans="1:11">
@@ -4968,7 +4990,7 @@
         <v>61</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>125</v>
@@ -4980,22 +5002,22 @@
         <v>127</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:11">
@@ -5018,7 +5040,7 @@
         <v>62</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>23</v>
@@ -5030,10 +5052,10 @@
         <v>15</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>238</v>
@@ -5042,10 +5064,10 @@
         <v>42</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="100" ht="32" customHeight="1" spans="1:11">
@@ -5053,7 +5075,7 @@
         <v>63</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>23</v>
@@ -5065,22 +5087,22 @@
         <v>56</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:11">
@@ -5088,7 +5110,7 @@
         <v>64</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>23</v>
@@ -5100,22 +5122,22 @@
         <v>56</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:11">
@@ -5138,7 +5160,7 @@
         <v>65</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>23</v>
@@ -5150,10 +5172,10 @@
         <v>31</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>196</v>
@@ -5162,10 +5184,10 @@
         <v>42</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:11">
@@ -5188,7 +5210,7 @@
         <v>66</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>30</v>
@@ -5200,22 +5222,22 @@
         <v>31</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" ht="32" customHeight="1" spans="1:11">
@@ -5223,7 +5245,7 @@
         <v>67</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>23</v>
@@ -5235,22 +5257,22 @@
         <v>31</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>233</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" ht="32" customHeight="1" spans="1:11">
@@ -5258,7 +5280,7 @@
         <v>68</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>30</v>
@@ -5270,22 +5292,22 @@
         <v>31</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:11">
@@ -5308,7 +5330,7 @@
         <v>69</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>23</v>
@@ -5320,22 +5342,22 @@
         <v>56</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="110" ht="32" customHeight="1" spans="1:11">
@@ -5343,34 +5365,34 @@
         <v>70</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>149</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5460,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:10">
@@ -5553,7 +5575,7 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -6007,7 +6029,7 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:10">
       <c r="A25" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6177,7 +6199,7 @@
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:10">
       <c r="A32" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6315,7 +6337,7 @@
     </row>
     <row r="38" ht="32" customHeight="1" spans="1:10">
       <c r="A38" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6378,7 +6400,7 @@
         <v>23</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>23</v>
@@ -6390,19 +6412,19 @@
         <v>56</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:10">
@@ -6424,7 +6446,7 @@
         <v>24</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>125</v>
@@ -6436,19 +6458,19 @@
         <v>127</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1" spans="1:10">
@@ -6456,7 +6478,7 @@
         <v>25</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>125</v>
@@ -6468,19 +6490,19 @@
         <v>127</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:10">
@@ -6502,7 +6524,7 @@
         <v>26</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>23</v>
@@ -6514,10 +6536,10 @@
         <v>31</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>196</v>
@@ -6526,12 +6548,12 @@
         <v>42</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:10">
       <c r="A47" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -6548,7 +6570,7 @@
         <v>27</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>30</v>
@@ -6560,19 +6582,19 @@
         <v>31</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1" spans="1:10">
@@ -6580,7 +6602,7 @@
         <v>28</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>23</v>
@@ -6592,19 +6614,19 @@
         <v>31</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>233</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6612,7 +6634,7 @@
         <v>29</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>30</v>
@@ -6624,19 +6646,19 @@
         <v>31</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6686,7 +6708,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -7229,7 +7251,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>125</v>
@@ -7241,19 +7263,19 @@
         <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>90</v>
@@ -7264,7 +7286,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
@@ -7276,19 +7298,19 @@
         <v>31</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>90</v>
@@ -7299,7 +7321,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
@@ -7311,19 +7333,19 @@
         <v>56</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>107</v>
@@ -7334,7 +7356,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
@@ -7346,19 +7368,19 @@
         <v>31</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>107</v>
@@ -7369,7 +7391,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
@@ -7381,19 +7403,19 @@
         <v>31</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>107</v>
@@ -7404,7 +7426,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>23</v>
@@ -7416,19 +7438,19 @@
         <v>56</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>107</v>
@@ -7467,7 +7489,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -7830,7 +7852,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>125</v>
@@ -7842,19 +7864,19 @@
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>220</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>66</v>
@@ -7865,7 +7887,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>23</v>
@@ -7877,7 +7899,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>42</v>
@@ -7889,7 +7911,7 @@
         <v>42</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>66</v>
@@ -7915,7 +7937,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -7927,19 +7949,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>66</v>
@@ -7950,7 +7972,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>30</v>
@@ -7962,19 +7984,19 @@
         <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>66</v>
@@ -7985,7 +8007,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
@@ -7997,19 +8019,19 @@
         <v>56</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>90</v>
@@ -8020,7 +8042,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
@@ -8035,7 +8057,7 @@
         <v>163</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>196</v>
@@ -8044,7 +8066,7 @@
         <v>42</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>90</v>
@@ -8055,7 +8077,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
@@ -8067,19 +8089,19 @@
         <v>149</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>90</v>
@@ -8090,7 +8112,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
@@ -8099,13 +8121,13 @@
         <v>174</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>163</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>196</v>
@@ -8114,7 +8136,7 @@
         <v>42</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>90</v>
@@ -8125,7 +8147,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>23</v>
@@ -8137,19 +8159,19 @@
         <v>15</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>107</v>
@@ -8160,7 +8182,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>23</v>
@@ -8172,19 +8194,19 @@
         <v>56</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>107</v>
@@ -8195,7 +8217,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>23</v>
@@ -8207,10 +8229,10 @@
         <v>15</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>238</v>
@@ -8219,7 +8241,7 @@
         <v>42</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>107</v>
@@ -8230,7 +8252,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>23</v>
@@ -8242,19 +8264,19 @@
         <v>56</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>107</v>
@@ -8265,7 +8287,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>23</v>
@@ -8277,19 +8299,19 @@
         <v>56</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>133</v>
@@ -8300,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>23</v>
@@ -8312,19 +8334,19 @@
         <v>56</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>133</v>
@@ -8335,31 +8357,31 @@
         <v>22</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>149</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>133</v>
@@ -8395,148 +8417,148 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5">
       <c r="A11" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B11" s="9">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5">
       <c r="A12" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/Database_Jadwal_Produksi.xlsx
+++ b/Database_Jadwal_Produksi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6590" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="6590" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="420">
   <si>
     <t>DIPAKSA MENIKAH - MASTER SCHEDULE (ALL 70 SUB-SCENES)</t>
   </si>
@@ -1176,22 +1176,34 @@
     <t>DIPAKSA MENIKAH - DAY 1 SHOOTING SCHEDULE (SCHOOL, EXPO &amp; PUBLIC SETS)</t>
   </si>
   <si>
-    <r>
-      <t>SET CATEGORY : AREA SEKOLAH &amp; EXPO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF2C3E50"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">				</t>
-    </r>
+    <t>SET CATEGORY: TAMAN, JALANAN, DAN BANDARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET CATEGORY: AREA SEKOLAH &amp; EXPO				</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RESTORAN RAMLI</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: KANTOR RICKO, KANTOR HENDRA DAN BANK</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RUMAH RAMLI / INTAN</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: SET MOBIL</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RUMAH RICKO - KAMAR RICKO</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
   </si>
   <si>
     <t>DIPAKSA MENIKAH - DAY 2 SHOOTING SCHEDULE (HOSPITAL &amp; VIP ROOMS)</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RUMAH SAKIT</t>
   </si>
   <si>
     <t>DIPAKSA MENIKAH - DAY 3 SHOOTING SCHEDULE (RAMLI/INTAN HOUSE &amp; AKAD)</t>
@@ -1291,7 +1303,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1474,13 +1486,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2C3E50"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -5497,7 +5502,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:10">
       <c r="A5" s="10" t="s">
-        <v>12</v>
+        <v>381</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5575,7 +5580,7 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -5813,7 +5818,7 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:10">
       <c r="A16" s="10" t="s">
-        <v>116</v>
+        <v>383</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5859,7 +5864,7 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:10">
       <c r="A18" s="10" t="s">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5937,7 +5942,7 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:10">
       <c r="A21" s="10" t="s">
-        <v>116</v>
+        <v>383</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5983,7 +5988,7 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:10">
       <c r="A23" s="10" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6029,7 +6034,7 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:10">
       <c r="A25" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6075,7 +6080,7 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:10">
       <c r="A27" s="10" t="s">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6121,7 +6126,7 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:10">
       <c r="A29" s="10" t="s">
-        <v>12</v>
+        <v>381</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6199,7 +6204,7 @@
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:10">
       <c r="A32" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6245,7 +6250,7 @@
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:10">
       <c r="A34" s="10" t="s">
-        <v>216</v>
+        <v>387</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6291,7 +6296,7 @@
     </row>
     <row r="36" ht="32" customHeight="1" spans="1:10">
       <c r="A36" s="10" t="s">
-        <v>222</v>
+        <v>388</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6337,7 +6342,7 @@
     </row>
     <row r="38" ht="32" customHeight="1" spans="1:10">
       <c r="A38" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6383,7 +6388,7 @@
     </row>
     <row r="40" ht="32" customHeight="1" spans="1:10">
       <c r="A40" s="10" t="s">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -6429,7 +6434,7 @@
     </row>
     <row r="42" ht="32" customHeight="1" spans="1:10">
       <c r="A42" s="10" t="s">
-        <v>222</v>
+        <v>388</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -6507,7 +6512,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:10">
       <c r="A45" s="10" t="s">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -6553,7 +6558,7 @@
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:10">
       <c r="A47" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -6708,7 +6713,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -6748,7 +6753,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>67</v>
+        <v>390</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7148,7 +7153,7 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:11">
       <c r="A17" s="10" t="s">
-        <v>12</v>
+        <v>381</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7198,7 +7203,7 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:11">
       <c r="A19" s="10" t="s">
-        <v>67</v>
+        <v>390</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7489,7 +7494,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -7529,7 +7534,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>12</v>
+        <v>381</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7579,7 +7584,7 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -7699,7 +7704,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:11">
       <c r="A11" s="10" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -7749,7 +7754,7 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:11">
       <c r="A13" s="10" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7834,7 +7839,7 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:11">
       <c r="A16" s="10" t="s">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7919,7 +7924,7 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:11">
       <c r="A19" s="10" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -8417,148 +8422,148 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5">
       <c r="A11" s="8" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B11" s="9">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E11" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5">
       <c r="A12" s="8" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D12" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E12" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/Database_Jadwal_Produksi.xlsx
+++ b/Database_Jadwal_Produksi.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="420">
   <si>
     <t>DIPAKSA MENIKAH - MASTER SCHEDULE (ALL 70 SUB-SCENES)</t>
   </si>
@@ -1176,37 +1176,37 @@
     <t>DIPAKSA MENIKAH - DAY 1 SHOOTING SCHEDULE (SCHOOL, EXPO &amp; PUBLIC SETS)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET CATEGORY: AREA SEKOLAH &amp; EXPO				</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RESTORAN RAMLI</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: KANTOR RICKO, KANTOR HENDRA DAN BANK</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: SET MOBIL</t>
+  </si>
+  <si>
     <t>SET CATEGORY: TAMAN, JALANAN, DAN BANDARA</t>
   </si>
   <si>
-    <t xml:space="preserve">SET CATEGORY: AREA SEKOLAH &amp; EXPO				</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: RESTORAN RAMLI</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: KANTOR RICKO, KANTOR HENDRA DAN BANK</t>
+    <t>SET CATEGORY: RUMAH RICKO - KAMAR RICKO</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
+  </si>
+  <si>
+    <t>DIPAKSA MENIKAH - DAY 2 SHOOTING SCHEDULE (HOSPITAL &amp; VIP ROOMS)</t>
+  </si>
+  <si>
+    <t>SET CATEGORY: RUMAH SAKIT</t>
+  </si>
+  <si>
+    <t>DIPAKSA MENIKAH - DAY 3 SHOOTING SCHEDULE (RAMLI/INTAN HOUSE &amp; AKAD)</t>
   </si>
   <si>
     <t>SET CATEGORY: RUMAH RAMLI / INTAN</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: SET MOBIL</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: RUMAH RICKO - KAMAR RICKO</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: LOKASI LAIN (CAFE MILAN, TOKO MAINAN, MINI MARKET)</t>
-  </si>
-  <si>
-    <t>DIPAKSA MENIKAH - DAY 2 SHOOTING SCHEDULE (HOSPITAL &amp; VIP ROOMS)</t>
-  </si>
-  <si>
-    <t>SET CATEGORY: RUMAH SAKIT</t>
-  </si>
-  <si>
-    <t>DIPAKSA MENIKAH - DAY 3 SHOOTING SCHEDULE (RAMLI/INTAN HOUSE &amp; AKAD)</t>
   </si>
   <si>
     <t>DIPAKSA MENIKAH - PRODUCTION SUMMARY &amp; CALL SHEET OVERVIEW</t>
@@ -5448,7 +5448,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:J50"/>
+  <dimension ref="A2:K46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5515,356 +5515,356 @@
       <c r="J5" s="11"/>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:10">
-      <c r="A6" s="5">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:10">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:10">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:10">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="F8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:10">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:10">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:10">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:10">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:10">
+      <c r="A13" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:10">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:10">
-      <c r="A8" s="10" t="s">
+      <c r="F14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:10">
+      <c r="A15" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:10">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:11">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:11">
+      <c r="A18" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:10">
-      <c r="A9" s="3">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:10">
-      <c r="A10" s="5">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:10">
-      <c r="A11" s="3">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" spans="1:10">
-      <c r="A12" s="5">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1" spans="1:10">
-      <c r="A13" s="3">
-        <v>7</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1" spans="1:10">
-      <c r="A14" s="5">
-        <v>8</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1" spans="1:10">
-      <c r="A15" s="3">
-        <v>9</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:10">
-      <c r="A16" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="32" customHeight="1" spans="1:10">
-      <c r="A17" s="3">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:10">
-      <c r="A18" s="10" t="s">
-        <v>384</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5876,165 +5876,168 @@
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" ht="32" customHeight="1" spans="1:10">
-      <c r="A19" s="3">
-        <v>11</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="3" t="s">
+    <row r="19" ht="32" customHeight="1" spans="1:11">
+      <c r="A19" s="5">
+        <v>13</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1" spans="1:10">
-      <c r="A20" s="5">
+      <c r="F19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:11">
+      <c r="A20" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:11">
+      <c r="A21" s="5">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:11">
+      <c r="A22" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" ht="32" customHeight="1" spans="1:11">
+      <c r="A23" s="5">
+        <v>16</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1" spans="1:11">
+      <c r="A24" s="5">
         <v>12</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:10">
-      <c r="A21" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" ht="32" customHeight="1" spans="1:10">
-      <c r="A22" s="5">
-        <v>13</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:10">
-      <c r="A23" s="10" t="s">
+      <c r="H24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1" spans="1:11">
+      <c r="A25" s="10" t="s">
         <v>385</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" ht="32" customHeight="1" spans="1:10">
-      <c r="A24" s="5">
-        <v>14</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:10">
-      <c r="A25" s="10" t="s">
-        <v>382</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6046,165 +6049,165 @@
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" ht="32" customHeight="1" spans="1:10">
-      <c r="A26" s="5">
+    <row r="26" ht="32" customHeight="1" spans="1:11">
+      <c r="A26" s="3">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:11">
+      <c r="A27" s="5">
+        <v>18</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="1:11">
+      <c r="A28" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:11">
+      <c r="A29" s="5">
+        <v>19</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:11">
+      <c r="A30" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:11">
+      <c r="A31" s="5">
+        <v>20</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:10">
-      <c r="A27" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" ht="32" customHeight="1" spans="1:10">
-      <c r="A28" s="5">
-        <v>16</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1" spans="1:10">
-      <c r="A29" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" ht="32" customHeight="1" spans="1:10">
-      <c r="A30" s="3">
-        <v>17</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:10">
-      <c r="A31" s="5">
-        <v>18</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" spans="1:10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1" spans="1:11">
       <c r="A32" s="10" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6218,39 +6221,39 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:10">
       <c r="A33" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>149</v>
+        <v>15</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:10">
       <c r="A34" s="10" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6264,39 +6267,39 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:10">
       <c r="A35" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1" spans="1:10">
       <c r="A36" s="10" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6308,41 +6311,41 @@
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
     </row>
-    <row r="37" ht="22" customHeight="1" spans="1:10">
+    <row r="37" ht="32" customHeight="1" spans="1:10">
       <c r="A37" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1" spans="1:10">
       <c r="A38" s="10" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6354,338 +6357,244 @@
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
     </row>
-    <row r="39" ht="22" customHeight="1" spans="1:10">
-      <c r="A39" s="5">
-        <v>22</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C39" s="5" t="s">
+    <row r="39" ht="32" customHeight="1" spans="1:10">
+      <c r="A39" s="3">
+        <v>24</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1" spans="1:10">
+      <c r="A40" s="5">
+        <v>25</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:10">
+      <c r="A41" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:10">
+      <c r="A42" s="3">
+        <v>26</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1" spans="1:10">
+      <c r="A43" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" ht="32" customHeight="1" spans="1:10">
+      <c r="A44" s="3">
+        <v>27</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1" spans="1:10">
+      <c r="A45" s="5">
+        <v>28</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I39" s="6" t="s">
+      <c r="F45" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1" spans="1:10">
-      <c r="A40" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" ht="32" customHeight="1" spans="1:10">
-      <c r="A41" s="5">
-        <v>23</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="J45" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="3">
+        <v>29</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1" spans="1:10">
-      <c r="A42" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" ht="32" customHeight="1" spans="1:10">
-      <c r="A43" s="3">
-        <v>24</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1" spans="1:10">
-      <c r="A44" s="5">
-        <v>25</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:10">
-      <c r="A45" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:10">
-      <c r="A46" s="3">
-        <v>26</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>288</v>
+        <v>367</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>196</v>
+        <v>337</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1" spans="1:10">
-      <c r="A47" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-    </row>
-    <row r="48" ht="32" customHeight="1" spans="1:10">
-      <c r="A48" s="3">
-        <v>27</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1" spans="1:10">
-      <c r="A49" s="5">
-        <v>28</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="3">
-        <v>29</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J50" s="4" t="s">
         <v>368</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A30:J30"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A36:J36"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A43:J43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6695,7 +6604,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K26"/>
+  <dimension ref="A2:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -6713,7 +6622,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -6753,7 +6662,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7153,7 +7062,7 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:11">
       <c r="A17" s="10" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7168,84 +7077,104 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:11">
       <c r="A18" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>174</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:11">
-      <c r="A19" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
+    <row r="19" ht="32" customHeight="1" spans="1:11">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:11">
       <c r="A20" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>174</v>
+        <v>14</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>92</v>
+        <v>264</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>209</v>
+        <v>267</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>90</v>
@@ -7253,45 +7182,45 @@
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:11">
       <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>254</v>
+        <v>42</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>42</v>
+        <v>271</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:11">
       <c r="A22" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
@@ -7306,27 +7235,27 @@
         <v>264</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:11">
       <c r="A23" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
@@ -7335,22 +7264,22 @@
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>107</v>
@@ -7358,107 +7287,122 @@
     </row>
     <row r="24" ht="32" customHeight="1" spans="1:11">
       <c r="A24" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>264</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1" spans="1:11">
-      <c r="A25" s="3">
-        <v>18</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C25" s="3" t="s">
+    <row r="25" ht="22" customHeight="1" spans="1:11">
+      <c r="A25" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" spans="1:11">
+      <c r="A26" s="3">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1" spans="1:11">
+      <c r="A27" s="5">
+        <v>9</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1" spans="1:11">
-      <c r="A26" s="5">
-        <v>19</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>107</v>
+      <c r="D27" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7410,7 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A25:K25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -7476,7 +7420,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K32"/>
+  <dimension ref="A2:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -7494,7 +7438,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11">
@@ -7532,9 +7476,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:11">
+    <row r="5" customFormat="1" ht="22" customHeight="1" spans="1:11">
       <c r="A5" s="10" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7545,208 +7489,221 @@
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:11">
+    </row>
+    <row r="6" customFormat="1" ht="32" customHeight="1" spans="1:11">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:11">
-      <c r="A7" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="32" customHeight="1" spans="1:11">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:11">
       <c r="A8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>157</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>161</v>
+        <v>36</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1" spans="1:11">
-      <c r="A9" s="3">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>21</v>
-      </c>
+    <row r="9" ht="22" customHeight="1" spans="1:11">
+      <c r="A9" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:11">
       <c r="A10" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>149</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:11">
-      <c r="A11" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:11">
+      <c r="A11" s="3">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:11">
       <c r="A12" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>174</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>45</v>
@@ -7754,7 +7711,7 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:11">
       <c r="A13" s="10" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7769,95 +7726,95 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:11">
       <c r="A14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:11">
-      <c r="A15" s="3">
-        <v>7</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="3" t="s">
+    <row r="15" ht="22" customHeight="1" spans="1:11">
+      <c r="A15" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:11">
+      <c r="A16" s="5">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="F16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:11">
-      <c r="A16" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:11">
       <c r="A17" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>125</v>
@@ -7869,538 +7826,549 @@
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:11">
+      <c r="A18" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:11">
+      <c r="A19" s="5">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1" spans="1:11">
-      <c r="A18" s="5">
-        <v>9</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="5" t="s">
+    <row r="20" ht="32" customHeight="1" spans="1:11">
+      <c r="A20" s="3">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:11">
+      <c r="A21" s="5">
+        <v>12</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:11">
+      <c r="A22" s="3">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1" spans="1:11">
+      <c r="A23" s="5">
+        <v>14</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1" spans="1:11">
+      <c r="A24" s="3">
         <v>15</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:11">
-      <c r="A19" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-    </row>
-    <row r="20" ht="32" customHeight="1" spans="1:11">
-      <c r="A20" s="5">
-        <v>10</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="I24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1" spans="1:11">
+      <c r="A25" s="5">
+        <v>16</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1" spans="1:11">
+      <c r="A26" s="3">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1" spans="1:11">
+      <c r="A27" s="5">
+        <v>18</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="1:11">
+      <c r="A28" s="3">
+        <v>19</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" spans="1:11">
+      <c r="A29" s="5">
+        <v>20</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:11">
+      <c r="A30" s="3">
+        <v>21</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1" spans="1:11">
-      <c r="A21" s="3">
-        <v>11</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1" spans="1:11">
-      <c r="A22" s="5">
-        <v>12</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="E30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1" spans="1:11">
+      <c r="A31" s="5">
+        <v>22</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1" spans="1:11">
-      <c r="A23" s="3">
-        <v>13</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1" spans="1:11">
-      <c r="A24" s="5">
+      <c r="D31" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="22" customHeight="1" spans="1:11">
+      <c r="A32" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" customFormat="1" ht="32" customHeight="1" spans="1:10">
+      <c r="A33" s="5">
         <v>14</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1" spans="1:11">
-      <c r="A25" s="3">
-        <v>15</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1" spans="1:11">
-      <c r="A26" s="5">
-        <v>16</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1" spans="1:11">
-      <c r="A27" s="3">
-        <v>17</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1" spans="1:11">
-      <c r="A28" s="5">
-        <v>18</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1" spans="1:11">
-      <c r="A29" s="3">
-        <v>19</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1" spans="1:11">
-      <c r="A30" s="5">
-        <v>20</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1" spans="1:11">
-      <c r="A31" s="3">
-        <v>21</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" spans="1:11">
-      <c r="A32" s="5">
-        <v>22</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>133</v>
+      <c r="B33" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:K9"/>
     <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A32:J32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
